--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -56,7 +56,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>

--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -56,7 +56,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,16 +76,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -494,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3242,7 +3232,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C87:F87</t>
+          <t>C92:F92</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3272,7 +3262,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C88:F88</t>
+          <t>C93:F93</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -3302,7 +3292,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C89:F89</t>
+          <t>C94:F94</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -3332,7 +3322,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C90:F90</t>
+          <t>C95:F95</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -3362,7 +3352,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C92:F92</t>
+          <t>C97:F97</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -3392,7 +3382,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C93:F93</t>
+          <t>C98:F98</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -3422,7 +3412,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C94:F94</t>
+          <t>C99:F99</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -3452,7 +3442,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C95:F95</t>
+          <t>C100:F100</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -3482,7 +3472,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C97:F97</t>
+          <t>C102:F102</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -3512,7 +3502,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C98:F98</t>
+          <t>C103:F103</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -3542,7 +3532,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C99:F99</t>
+          <t>C104:F104</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -3572,7 +3562,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C100:F100</t>
+          <t>C105:F105</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -3602,7 +3592,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B102:F102</t>
+          <t>B107:F107</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -3632,7 +3622,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B103:F103</t>
+          <t>B108:F108</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -3962,7 +3952,7 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>B82:F82</t>
+          <t>B87:F87</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -3992,12 +3982,72 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
+          <t>B88:F88</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>lease_repayments, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="n">
+        <v>124</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>B82:F82</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
           <t>B83:F83</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>lease_repayments, revenue_link</t>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex, revenue_link</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9938,41 +9988,41 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>LEASE REPAYMENT CONTEXT</t>
+          <t>OPERATING CASH AFTER PP&amp;E CAPEX</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>Repayments of Lease Liabilities (reported)</t>
+          <t>Operating Cash Flow (reported)</t>
         </is>
       </c>
       <c r="B81" s="13">
-        <f>'Cash Flow Statement'!B47</f>
+        <f>'Cash Flow Statement'!B30</f>
         <v/>
       </c>
       <c r="C81" s="13">
-        <f>'Cash Flow Statement'!C47</f>
+        <f>'Cash Flow Statement'!C30</f>
         <v/>
       </c>
       <c r="D81" s="13">
-        <f>'Cash Flow Statement'!D47</f>
+        <f>'Cash Flow Statement'!D30</f>
         <v/>
       </c>
       <c r="E81" s="13">
-        <f>'Cash Flow Statement'!E47</f>
+        <f>'Cash Flow Statement'!E30</f>
         <v/>
       </c>
       <c r="F81" s="13">
-        <f>'Cash Flow Statement'!F47</f>
+        <f>'Cash Flow Statement'!F30</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="B82" s="16" t="n"/>
@@ -9984,7 +10034,7 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="B83" s="15" t="n"/>
@@ -9996,43 +10046,44 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>LEASE REPAYMENT CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Repayments of Lease Liabilities (reported)</t>
         </is>
       </c>
       <c r="B86" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Cash Flow Statement'!B47</f>
         <v/>
       </c>
       <c r="C86" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Cash Flow Statement'!C47</f>
         <v/>
       </c>
       <c r="D86" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Cash Flow Statement'!D47</f>
         <v/>
       </c>
       <c r="E86" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Cash Flow Statement'!E47</f>
         <v/>
       </c>
       <c r="F86" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Cash Flow Statement'!F47</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="n"/>
       <c r="C87" s="16" t="n"/>
       <c r="D87" s="16" t="n"/>
       <c r="E87" s="16" t="n"/>
@@ -10041,67 +10092,53 @@
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n"/>
       <c r="C88" s="15" t="n"/>
       <c r="D88" s="15" t="n"/>
       <c r="E88" s="15" t="n"/>
       <c r="F88" s="15" t="n"/>
     </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="n"/>
-      <c r="D89" s="16" t="n"/>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="n"/>
-    </row>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="15" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>'Balance Sheet'!B38</f>
+        <f>'Balance Sheet'!B37</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>'Balance Sheet'!C38</f>
+        <f>'Balance Sheet'!C37</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>'Balance Sheet'!D38</f>
+        <f>'Balance Sheet'!D37</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>'Balance Sheet'!E38</f>
+        <f>'Balance Sheet'!E37</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>'Balance Sheet'!F38</f>
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Goodwill</t>
         </is>
       </c>
       <c r="C92" s="16" t="n"/>
@@ -10112,7 +10149,7 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Goodwill Growth</t>
         </is>
       </c>
       <c r="C93" s="15" t="n"/>
@@ -10123,7 +10160,7 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C94" s="16" t="n"/>
@@ -10134,7 +10171,7 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C95" s="15" t="n"/>
@@ -10145,34 +10182,34 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Intangible Assets</t>
         </is>
       </c>
       <c r="B96" s="13">
-        <f>B86+B91</f>
+        <f>'Balance Sheet'!B38</f>
         <v/>
       </c>
       <c r="C96" s="13">
-        <f>C86+C91</f>
+        <f>'Balance Sheet'!C38</f>
         <v/>
       </c>
       <c r="D96" s="13">
-        <f>D86+D91</f>
+        <f>'Balance Sheet'!D38</f>
         <v/>
       </c>
       <c r="E96" s="13">
-        <f>E86+E91</f>
+        <f>'Balance Sheet'!E38</f>
         <v/>
       </c>
       <c r="F96" s="13">
-        <f>F86+F91</f>
+        <f>'Balance Sheet'!F38</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Change in Intangible Assets</t>
         </is>
       </c>
       <c r="C97" s="16" t="n"/>
@@ -10183,7 +10220,7 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Intangible Assets Growth</t>
         </is>
       </c>
       <c r="C98" s="15" t="n"/>
@@ -10194,7 +10231,7 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C99" s="16" t="n"/>
@@ -10205,7 +10242,7 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C100" s="15" t="n"/>
@@ -10216,37 +10253,36 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
+          <t>Goodwill &amp; Intangibles</t>
         </is>
       </c>
       <c r="B101" s="13">
-        <f>'Cash Flow Statement'!B38</f>
+        <f>B91+B96</f>
         <v/>
       </c>
       <c r="C101" s="13">
-        <f>'Cash Flow Statement'!C38</f>
+        <f>C91+C96</f>
         <v/>
       </c>
       <c r="D101" s="13">
-        <f>'Cash Flow Statement'!D38</f>
+        <f>D91+D96</f>
         <v/>
       </c>
       <c r="E101" s="13">
-        <f>'Cash Flow Statement'!E38</f>
+        <f>E91+E96</f>
         <v/>
       </c>
       <c r="F101" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+        <f>F91+F96</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="n"/>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
       <c r="C102" s="16" t="n"/>
       <c r="D102" s="16" t="n"/>
       <c r="E102" s="16" t="n"/>
@@ -10255,14 +10291,86 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments / Revenue</t>
-        </is>
-      </c>
-      <c r="B103" s="15" t="n"/>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
       <c r="C103" s="15" t="n"/>
       <c r="D103" s="15" t="n"/>
       <c r="E103" s="15" t="n"/>
       <c r="F103" s="15" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="n"/>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="16" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="n"/>
+      <c r="D105" s="15" t="n"/>
+      <c r="E105" s="15" t="n"/>
+      <c r="F105" s="15" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B106" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C106" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D106" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F106" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="n"/>
+      <c r="C107" s="16" t="n"/>
+      <c r="D107" s="16" t="n"/>
+      <c r="E107" s="16" t="n"/>
+      <c r="F107" s="16" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments / Revenue</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C92:F92</t>
+          <t>C105:F105</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C93:F93</t>
+          <t>C106:F106</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C94:F94</t>
+          <t>C107:F107</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C95:F95</t>
+          <t>C108:F108</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C97:F97</t>
+          <t>C110:F110</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C98:F98</t>
+          <t>C111:F111</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C99:F99</t>
+          <t>C112:F112</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C100:F100</t>
+          <t>C113:F113</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C102:F102</t>
+          <t>C115:F115</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C103:F103</t>
+          <t>C116:F116</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C104:F104</t>
+          <t>C117:F117</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C105:F105</t>
+          <t>C118:F118</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B107:F107</t>
+          <t>B120:F120</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B108:F108</t>
+          <t>B121:F121</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -4048,6 +4048,126 @@
       <c r="F121" s="11" t="inlineStr">
         <is>
           <t>cash_after_ppe_capex, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>B95:F95</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>B97:F97</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="n">
+        <v>137</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>B99:F99</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>B101:F101</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10104,114 +10224,164 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>CASH ROLL-FORWARD CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Net cash from operating activities (reported)</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Cash Flow Statement'!B30</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Cash Flow Statement'!C30</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Cash Flow Statement'!D30</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Cash Flow Statement'!E30</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Cash Flow Statement'!F30</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="n"/>
-      <c r="D92" s="16" t="n"/>
-      <c r="E92" s="16" t="n"/>
-      <c r="F92" s="16" t="n"/>
+          <t>Net cash from investing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B92" s="13">
+        <f>'Cash Flow Statement'!B32</f>
+        <v/>
+      </c>
+      <c r="C92" s="13">
+        <f>'Cash Flow Statement'!C32</f>
+        <v/>
+      </c>
+      <c r="D92" s="13">
+        <f>'Cash Flow Statement'!D32</f>
+        <v/>
+      </c>
+      <c r="E92" s="13">
+        <f>'Cash Flow Statement'!E32</f>
+        <v/>
+      </c>
+      <c r="F92" s="13">
+        <f>'Cash Flow Statement'!F32</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="n"/>
-      <c r="D93" s="15" t="n"/>
-      <c r="E93" s="15" t="n"/>
-      <c r="F93" s="15" t="n"/>
+          <t>Net cash from financing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B93" s="13">
+        <f>'Cash Flow Statement'!B31</f>
+        <v/>
+      </c>
+      <c r="C93" s="13">
+        <f>'Cash Flow Statement'!C31</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>'Cash Flow Statement'!D31</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>'Cash Flow Statement'!E31</f>
+        <v/>
+      </c>
+      <c r="F93" s="13">
+        <f>'Cash Flow Statement'!F31</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="16" t="n"/>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="n"/>
+          <t>Effect of FX on cash (reported)</t>
+        </is>
+      </c>
+      <c r="B94" s="13">
+        <f>'Cash Flow Statement'!B18</f>
+        <v/>
+      </c>
+      <c r="C94" s="13">
+        <f>'Cash Flow Statement'!C18</f>
+        <v/>
+      </c>
+      <c r="D94" s="13">
+        <f>'Cash Flow Statement'!D18</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>'Cash Flow Statement'!E18</f>
+        <v/>
+      </c>
+      <c r="F94" s="13">
+        <f>'Cash Flow Statement'!F18</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="n"/>
-      <c r="D95" s="15" t="n"/>
-      <c r="E95" s="15" t="n"/>
-      <c r="F95" s="15" t="n"/>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="n"/>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n"/>
+      <c r="E95" s="16" t="n"/>
+      <c r="F95" s="16" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Reported cash change</t>
         </is>
       </c>
       <c r="B96" s="13">
-        <f>'Balance Sheet'!B38</f>
+        <f>'Cash Flow Statement'!B33</f>
         <v/>
       </c>
       <c r="C96" s="13">
-        <f>'Balance Sheet'!C38</f>
+        <f>'Cash Flow Statement'!C33</f>
         <v/>
       </c>
       <c r="D96" s="13">
-        <f>'Balance Sheet'!D38</f>
+        <f>'Cash Flow Statement'!D33</f>
         <v/>
       </c>
       <c r="E96" s="13">
-        <f>'Balance Sheet'!E38</f>
+        <f>'Cash Flow Statement'!E33</f>
         <v/>
       </c>
       <c r="F96" s="13">
-        <f>'Balance Sheet'!F38</f>
+        <f>'Cash Flow Statement'!F33</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="B97" s="16" t="n"/>
       <c r="C97" s="16" t="n"/>
       <c r="D97" s="16" t="n"/>
       <c r="E97" s="16" t="n"/>
@@ -10220,20 +10390,37 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="n"/>
-      <c r="D98" s="15" t="n"/>
-      <c r="E98" s="15" t="n"/>
-      <c r="F98" s="15" t="n"/>
+          <t>Cash beginning (reported)</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>'Cash Flow Statement'!B12</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>'Cash Flow Statement'!C12</f>
+        <v/>
+      </c>
+      <c r="D98" s="13">
+        <f>'Cash Flow Statement'!D12</f>
+        <v/>
+      </c>
+      <c r="E98" s="13">
+        <f>'Cash Flow Statement'!E12</f>
+        <v/>
+      </c>
+      <c r="F98" s="13">
+        <f>'Cash Flow Statement'!F12</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="n"/>
       <c r="C99" s="16" t="n"/>
       <c r="D99" s="16" t="n"/>
       <c r="E99" s="16" t="n"/>
@@ -10242,119 +10429,104 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="n"/>
-      <c r="D100" s="15" t="n"/>
-      <c r="E100" s="15" t="n"/>
-      <c r="F100" s="15" t="n"/>
+          <t>Cash ending (reported)</t>
+        </is>
+      </c>
+      <c r="B100" s="13">
+        <f>'Cash Flow Statement'!B13</f>
+        <v/>
+      </c>
+      <c r="C100" s="13">
+        <f>'Cash Flow Statement'!C13</f>
+        <v/>
+      </c>
+      <c r="D100" s="13">
+        <f>'Cash Flow Statement'!D13</f>
+        <v/>
+      </c>
+      <c r="E100" s="13">
+        <f>'Cash Flow Statement'!E13</f>
+        <v/>
+      </c>
+      <c r="F100" s="13">
+        <f>'Cash Flow Statement'!F13</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>B91+B96</f>
-        <v/>
-      </c>
-      <c r="C101" s="13">
-        <f>C91+C96</f>
-        <v/>
-      </c>
-      <c r="D101" s="13">
-        <f>D91+D96</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>E91+E96</f>
-        <v/>
-      </c>
-      <c r="F101" s="13">
-        <f>F91+F96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="16" t="n"/>
-      <c r="E102" s="16" t="n"/>
-      <c r="F102" s="16" t="n"/>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="n"/>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="n"/>
+      <c r="E101" s="16" t="n"/>
+      <c r="F101" s="16" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C103" s="15" t="n"/>
-      <c r="D103" s="15" t="n"/>
-      <c r="E103" s="15" t="n"/>
-      <c r="F103" s="15" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="n"/>
-      <c r="D104" s="16" t="n"/>
-      <c r="E104" s="16" t="n"/>
-      <c r="F104" s="16" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B104" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C104" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D104" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E104" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F104" s="13">
+        <f>'Balance Sheet'!F37</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="n"/>
-      <c r="D105" s="15" t="n"/>
-      <c r="E105" s="15" t="n"/>
-      <c r="F105" s="15" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="n"/>
+      <c r="D105" s="16" t="n"/>
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="16" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B106" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C106" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D106" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E106" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F106" s="13">
-        <f>'Cash Flow Statement'!F38</f>
-        <v/>
-      </c>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="n"/>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
       <c r="C107" s="16" t="n"/>
       <c r="D107" s="16" t="n"/>
       <c r="E107" s="16" t="n"/>
@@ -10363,14 +10535,206 @@
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments / Revenue</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="n"/>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
       <c r="C108" s="15" t="n"/>
       <c r="D108" s="15" t="n"/>
       <c r="E108" s="15" t="n"/>
       <c r="F108" s="15" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C109" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D109" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E109" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F109" s="13">
+        <f>'Balance Sheet'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="n"/>
+      <c r="D110" s="16" t="n"/>
+      <c r="E110" s="16" t="n"/>
+      <c r="F110" s="16" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="15" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="n"/>
+      <c r="D112" s="16" t="n"/>
+      <c r="E112" s="16" t="n"/>
+      <c r="F112" s="16" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="n"/>
+      <c r="D113" s="15" t="n"/>
+      <c r="E113" s="15" t="n"/>
+      <c r="F113" s="15" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B114" s="13">
+        <f>B104+B109</f>
+        <v/>
+      </c>
+      <c r="C114" s="13">
+        <f>C104+C109</f>
+        <v/>
+      </c>
+      <c r="D114" s="13">
+        <f>D104+D109</f>
+        <v/>
+      </c>
+      <c r="E114" s="13">
+        <f>E104+E109</f>
+        <v/>
+      </c>
+      <c r="F114" s="13">
+        <f>F104+F109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="n"/>
+      <c r="D115" s="16" t="n"/>
+      <c r="E115" s="16" t="n"/>
+      <c r="F115" s="16" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="15" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="n"/>
+      <c r="D117" s="16" t="n"/>
+      <c r="E117" s="16" t="n"/>
+      <c r="F117" s="16" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="15" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B119" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C119" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D119" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E119" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F119" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="n"/>
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="16" t="n"/>
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="16" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments / Revenue</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+      <c r="F121" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C105:F105</t>
+          <t>C116:F116</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C106:F106</t>
+          <t>C117:F117</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C107:F107</t>
+          <t>C118:F118</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C108:F108</t>
+          <t>C119:F119</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C110:F110</t>
+          <t>C121:F121</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C111:F111</t>
+          <t>C122:F122</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C112:F112</t>
+          <t>C123:F123</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C113:F113</t>
+          <t>C124:F124</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C115:F115</t>
+          <t>C126:F126</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C116:F116</t>
+          <t>C127:F127</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C117:F117</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C118:F118</t>
+          <t>C129:F129</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B120:F120</t>
+          <t>B131:F131</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B121:F121</t>
+          <t>B132:F132</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -4168,6 +4168,186 @@
       <c r="F125" s="11" t="inlineStr">
         <is>
           <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>B107:F107</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>B108:F108</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>B109:F109</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>C110:F110</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="n">
+        <v>143</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>C111:F111</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="n">
+        <v>144</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>C112:F112</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>gross_margin_change, net_operating_expense_burden_change</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10468,76 +10648,110 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>REPORTED MARGIN BRIDGE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Revenue (reported)</t>
         </is>
       </c>
       <c r="B104" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Income Statement'!B21</f>
         <v/>
       </c>
       <c r="C104" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Income Statement'!C21</f>
         <v/>
       </c>
       <c r="D104" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Income Statement'!D21</f>
         <v/>
       </c>
       <c r="E104" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Income Statement'!E21</f>
         <v/>
       </c>
       <c r="F104" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="n"/>
+          <t>Gross profit (reported)</t>
+        </is>
+      </c>
+      <c r="B105" s="13">
+        <f>'Income Statement'!B12</f>
+        <v/>
+      </c>
+      <c r="C105" s="13">
+        <f>'Income Statement'!C12</f>
+        <v/>
+      </c>
+      <c r="D105" s="13">
+        <f>'Income Statement'!D12</f>
+        <v/>
+      </c>
+      <c r="E105" s="13">
+        <f>'Income Statement'!E12</f>
+        <v/>
+      </c>
+      <c r="F105" s="13">
+        <f>'Income Statement'!F12</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="n"/>
-      <c r="D106" s="15" t="n"/>
-      <c r="E106" s="15" t="n"/>
-      <c r="F106" s="15" t="n"/>
+          <t>Operating profit (reported)</t>
+        </is>
+      </c>
+      <c r="B106" s="13">
+        <f>'Income Statement'!B15</f>
+        <v/>
+      </c>
+      <c r="C106" s="13">
+        <f>'Income Statement'!C15</f>
+        <v/>
+      </c>
+      <c r="D106" s="13">
+        <f>'Income Statement'!D15</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>'Income Statement'!E15</f>
+        <v/>
+      </c>
+      <c r="F106" s="13">
+        <f>'Income Statement'!F15</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="16" t="n"/>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="n"/>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="n"/>
+      <c r="C107" s="15" t="n"/>
+      <c r="D107" s="15" t="n"/>
+      <c r="E107" s="15" t="n"/>
+      <c r="F107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n"/>
       <c r="C108" s="15" t="n"/>
       <c r="D108" s="15" t="n"/>
       <c r="E108" s="15" t="n"/>
@@ -10546,45 +10760,30 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B109" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C109" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D109" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E109" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F109" s="13">
-        <f>'Balance Sheet'!F38</f>
-        <v/>
-      </c>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="n"/>
+      <c r="C109" s="15" t="n"/>
+      <c r="D109" s="15" t="n"/>
+      <c r="E109" s="15" t="n"/>
+      <c r="F109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="n"/>
-      <c r="D110" s="16" t="n"/>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="16" t="n"/>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="15" t="n"/>
+      <c r="E110" s="15" t="n"/>
+      <c r="F110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Change in net operating expense burden</t>
         </is>
       </c>
       <c r="C111" s="15" t="n"/>
@@ -10595,146 +10794,284 @@
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="n"/>
-      <c r="D112" s="16" t="n"/>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="16" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C113" s="15" t="n"/>
-      <c r="D113" s="15" t="n"/>
-      <c r="E113" s="15" t="n"/>
-      <c r="F113" s="15" t="n"/>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="n"/>
+      <c r="D112" s="15" t="n"/>
+      <c r="E112" s="15" t="n"/>
+      <c r="F112" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>B104+B109</f>
-        <v/>
-      </c>
-      <c r="C114" s="13">
-        <f>C104+C109</f>
-        <v/>
-      </c>
-      <c r="D114" s="13">
-        <f>D104+D109</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>E104+E109</f>
-        <v/>
-      </c>
-      <c r="F114" s="13">
-        <f>F104+F109</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="n"/>
-      <c r="D115" s="16" t="n"/>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="16" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B115" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C115" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D115" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E115" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F115" s="13">
+        <f>'Balance Sheet'!F37</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="n"/>
-      <c r="D116" s="15" t="n"/>
-      <c r="E116" s="15" t="n"/>
-      <c r="F116" s="15" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="n"/>
+      <c r="D116" s="16" t="n"/>
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="n"/>
-      <c r="D117" s="16" t="n"/>
-      <c r="E117" s="16" t="n"/>
-      <c r="F117" s="16" t="n"/>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="n"/>
+      <c r="D117" s="15" t="n"/>
+      <c r="E117" s="15" t="n"/>
+      <c r="F117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
-      <c r="F118" s="15" t="n"/>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="n"/>
+      <c r="D118" s="16" t="n"/>
+      <c r="E118" s="16" t="n"/>
+      <c r="F118" s="16" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B119" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C119" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D119" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E119" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F119" s="13">
-        <f>'Cash Flow Statement'!F38</f>
-        <v/>
-      </c>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="n"/>
+      <c r="D119" s="15" t="n"/>
+      <c r="E119" s="15" t="n"/>
+      <c r="F119" s="15" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="n"/>
-      <c r="C120" s="16" t="n"/>
-      <c r="D120" s="16" t="n"/>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="16" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B120" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C120" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D120" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E120" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F120" s="13">
+        <f>'Balance Sheet'!F38</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="n"/>
+      <c r="D121" s="16" t="n"/>
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="16" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="15" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="n"/>
+      <c r="D123" s="16" t="n"/>
+      <c r="E123" s="16" t="n"/>
+      <c r="F123" s="16" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="n"/>
+      <c r="D124" s="15" t="n"/>
+      <c r="E124" s="15" t="n"/>
+      <c r="F124" s="15" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B125" s="13">
+        <f>B115+B120</f>
+        <v/>
+      </c>
+      <c r="C125" s="13">
+        <f>C115+C120</f>
+        <v/>
+      </c>
+      <c r="D125" s="13">
+        <f>D115+D120</f>
+        <v/>
+      </c>
+      <c r="E125" s="13">
+        <f>E115+E120</f>
+        <v/>
+      </c>
+      <c r="F125" s="13">
+        <f>F115+F120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="n"/>
+      <c r="D126" s="16" t="n"/>
+      <c r="E126" s="16" t="n"/>
+      <c r="F126" s="16" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="n"/>
+      <c r="D127" s="15" t="n"/>
+      <c r="E127" s="15" t="n"/>
+      <c r="F127" s="15" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="n"/>
+      <c r="D128" s="16" t="n"/>
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="16" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15" t="n"/>
+      <c r="E129" s="15" t="n"/>
+      <c r="F129" s="15" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B130" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C130" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D130" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E130" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F130" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="n"/>
+      <c r="C131" s="16" t="n"/>
+      <c r="D131" s="16" t="n"/>
+      <c r="E131" s="16" t="n"/>
+      <c r="F131" s="16" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
           <t>Intangible Payments / Revenue</t>
         </is>
       </c>
-      <c r="B121" s="15" t="n"/>
-      <c r="C121" s="15" t="n"/>
-      <c r="D121" s="15" t="n"/>
-      <c r="E121" s="15" t="n"/>
-      <c r="F121" s="15" t="n"/>
+      <c r="B132" s="15" t="n"/>
+      <c r="C132" s="15" t="n"/>
+      <c r="D132" s="15" t="n"/>
+      <c r="E132" s="15" t="n"/>
+      <c r="F132" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C116:F116</t>
+          <t>C125:F125</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C117:F117</t>
+          <t>C126:F126</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C118:F118</t>
+          <t>C127:F127</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C119:F119</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C121:F121</t>
+          <t>C130:F130</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C122:F122</t>
+          <t>C131:F131</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C123:F123</t>
+          <t>C132:F132</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C124:F124</t>
+          <t>C133:F133</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C126:F126</t>
+          <t>C135:F135</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C127:F127</t>
+          <t>C136:F136</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C128:F128</t>
+          <t>C137:F137</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C129:F129</t>
+          <t>C138:F138</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B131:F131</t>
+          <t>B140:F140</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B132:F132</t>
+          <t>B141:F141</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -4348,6 +4348,156 @@
       <c r="F131" s="11" t="inlineStr">
         <is>
           <t>gross_margin_change, net_operating_expense_burden_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>B117:F117</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="n">
+        <v>146</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>C118:F118</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="n">
+        <v>147</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>C119:F119</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>C120:F120</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="n">
+        <v>149</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>C121:F121</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10805,54 +10955,71 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>INVENTORY GROWTH AND INTENSITY CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Inventory (reported)</t>
         </is>
       </c>
       <c r="B115" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Balance Sheet'!B11</f>
         <v/>
       </c>
       <c r="C115" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Balance Sheet'!C11</f>
         <v/>
       </c>
       <c r="D115" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Balance Sheet'!D11</f>
         <v/>
       </c>
       <c r="E115" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Balance Sheet'!E11</f>
         <v/>
       </c>
       <c r="F115" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Balance Sheet'!F11</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="n"/>
-      <c r="D116" s="16" t="n"/>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="16" t="n"/>
+          <t>Revenue (reported)</t>
+        </is>
+      </c>
+      <c r="B116" s="13">
+        <f>'Income Statement'!B21</f>
+        <v/>
+      </c>
+      <c r="C116" s="13">
+        <f>'Income Statement'!C21</f>
+        <v/>
+      </c>
+      <c r="D116" s="13">
+        <f>'Income Statement'!D21</f>
+        <v/>
+      </c>
+      <c r="E116" s="13">
+        <f>'Income Statement'!E21</f>
+        <v/>
+      </c>
+      <c r="F116" s="13">
+        <f>'Income Statement'!F21</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="n"/>
       <c r="C117" s="15" t="n"/>
       <c r="D117" s="15" t="n"/>
       <c r="E117" s="15" t="n"/>
@@ -10861,7 +11028,7 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
+          <t>Change in inventory</t>
         </is>
       </c>
       <c r="C118" s="16" t="n"/>
@@ -10872,45 +11039,29 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C119" s="15" t="n"/>
-      <c r="D119" s="15" t="n"/>
-      <c r="E119" s="15" t="n"/>
-      <c r="F119" s="15" t="n"/>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="n"/>
+      <c r="D119" s="16" t="n"/>
+      <c r="E119" s="16" t="n"/>
+      <c r="F119" s="16" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B120" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C120" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D120" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E120" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F120" s="13">
-        <f>'Balance Sheet'!F38</f>
-        <v/>
-      </c>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="16" t="n"/>
+      <c r="E120" s="16" t="n"/>
+      <c r="F120" s="16" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Reconstructed change in inventory</t>
         </is>
       </c>
       <c r="C121" s="16" t="n"/>
@@ -10918,160 +11069,276 @@
       <c r="E121" s="16" t="n"/>
       <c r="F121" s="16" t="n"/>
     </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="n"/>
-      <c r="D122" s="15" t="n"/>
-      <c r="E122" s="15" t="n"/>
-      <c r="F122" s="15" t="n"/>
-    </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="n"/>
-      <c r="D123" s="16" t="n"/>
-      <c r="E123" s="16" t="n"/>
-      <c r="F123" s="16" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="n"/>
-      <c r="D124" s="15" t="n"/>
-      <c r="E124" s="15" t="n"/>
-      <c r="F124" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B124" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C124" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D124" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E124" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F124" s="13">
+        <f>'Balance Sheet'!F37</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B125" s="13">
-        <f>B115+B120</f>
-        <v/>
-      </c>
-      <c r="C125" s="13">
-        <f>C115+C120</f>
-        <v/>
-      </c>
-      <c r="D125" s="13">
-        <f>D115+D120</f>
-        <v/>
-      </c>
-      <c r="E125" s="13">
-        <f>E115+E120</f>
-        <v/>
-      </c>
-      <c r="F125" s="13">
-        <f>F115+F120</f>
-        <v/>
-      </c>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="n"/>
+      <c r="D125" s="16" t="n"/>
+      <c r="E125" s="16" t="n"/>
+      <c r="F125" s="16" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="n"/>
-      <c r="D126" s="16" t="n"/>
-      <c r="E126" s="16" t="n"/>
-      <c r="F126" s="16" t="n"/>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="15" t="n"/>
+      <c r="E126" s="15" t="n"/>
+      <c r="F126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C127" s="15" t="n"/>
-      <c r="D127" s="15" t="n"/>
-      <c r="E127" s="15" t="n"/>
-      <c r="F127" s="15" t="n"/>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C127" s="16" t="n"/>
+      <c r="D127" s="16" t="n"/>
+      <c r="E127" s="16" t="n"/>
+      <c r="F127" s="16" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="n"/>
-      <c r="D128" s="16" t="n"/>
-      <c r="E128" s="16" t="n"/>
-      <c r="F128" s="16" t="n"/>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C129" s="15" t="n"/>
-      <c r="D129" s="15" t="n"/>
-      <c r="E129" s="15" t="n"/>
-      <c r="F129" s="15" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B129" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C129" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D129" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E129" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F129" s="13">
+        <f>'Balance Sheet'!F38</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B130" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C130" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D130" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E130" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F130" s="13">
-        <f>'Cash Flow Statement'!F38</f>
-        <v/>
-      </c>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="n"/>
+      <c r="D130" s="16" t="n"/>
+      <c r="E130" s="16" t="n"/>
+      <c r="F130" s="16" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="n"/>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="n"/>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="16" t="n"/>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15" t="n"/>
+      <c r="E131" s="15" t="n"/>
+      <c r="F131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="n"/>
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="16" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="n"/>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
+      <c r="F133" s="15" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B134" s="13">
+        <f>B124+B129</f>
+        <v/>
+      </c>
+      <c r="C134" s="13">
+        <f>C124+C129</f>
+        <v/>
+      </c>
+      <c r="D134" s="13">
+        <f>D124+D129</f>
+        <v/>
+      </c>
+      <c r="E134" s="13">
+        <f>E124+E129</f>
+        <v/>
+      </c>
+      <c r="F134" s="13">
+        <f>F124+F129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="n"/>
+      <c r="D135" s="16" t="n"/>
+      <c r="E135" s="16" t="n"/>
+      <c r="F135" s="16" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="n"/>
+      <c r="D136" s="15" t="n"/>
+      <c r="E136" s="15" t="n"/>
+      <c r="F136" s="15" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="n"/>
+      <c r="E137" s="16" t="n"/>
+      <c r="F137" s="16" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="15" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B139" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C139" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D139" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E139" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F139" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="n"/>
+      <c r="C140" s="16" t="n"/>
+      <c r="D140" s="16" t="n"/>
+      <c r="E140" s="16" t="n"/>
+      <c r="F140" s="16" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
           <t>Intangible Payments / Revenue</t>
         </is>
       </c>
-      <c r="B132" s="15" t="n"/>
-      <c r="C132" s="15" t="n"/>
-      <c r="D132" s="15" t="n"/>
-      <c r="E132" s="15" t="n"/>
-      <c r="F132" s="15" t="n"/>
+      <c r="B141" s="15" t="n"/>
+      <c r="C141" s="15" t="n"/>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+      <c r="F141" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/fast_retailing/FastRetailing_Trainer.xlsx
+++ b/release/fast_retailing/FastRetailing_Trainer.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C125:F125</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C126:F126</t>
+          <t>C129:F129</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C127:F127</t>
+          <t>C130:F130</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C128:F128</t>
+          <t>C131:F131</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C130:F130</t>
+          <t>C133:F133</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C131:F131</t>
+          <t>C134:F134</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C132:F132</t>
+          <t>C135:F135</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C133:F133</t>
+          <t>C136:F136</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C135:F135</t>
+          <t>C138:F138</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C136:F136</t>
+          <t>C139:F139</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C137:F137</t>
+          <t>C140:F140</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C138:F138</t>
+          <t>C141:F141</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B140:F140</t>
+          <t>B143:F143</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B141:F141</t>
+          <t>B144:F144</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -4498,6 +4498,66 @@
       <c r="F136" s="11" t="inlineStr">
         <is>
           <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>C123:F123</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="n">
+        <v>151</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>C124:F124</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -11069,115 +11129,115 @@
       <c r="E121" s="16" t="n"/>
       <c r="F121" s="16" t="n"/>
     </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Inventory CF adjustment (reported)</t>
+        </is>
+      </c>
+      <c r="B122" s="13">
+        <f>'Cash Flow Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C122" s="13">
+        <f>'Cash Flow Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D122" s="13">
+        <f>'Cash Flow Statement'!D7</f>
+        <v/>
+      </c>
+      <c r="E122" s="13">
+        <f>'Cash Flow Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="F122" s="13">
+        <f>'Cash Flow Statement'!F7</f>
+        <v/>
+      </c>
+    </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
-      </c>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="n"/>
+      <c r="D123" s="16" t="n"/>
+      <c r="E123" s="16" t="n"/>
+      <c r="F123" s="16" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B124" s="13">
-        <f>'Balance Sheet'!B37</f>
-        <v/>
-      </c>
-      <c r="C124" s="13">
-        <f>'Balance Sheet'!C37</f>
-        <v/>
-      </c>
-      <c r="D124" s="13">
-        <f>'Balance Sheet'!D37</f>
-        <v/>
-      </c>
-      <c r="E124" s="13">
-        <f>'Balance Sheet'!E37</f>
-        <v/>
-      </c>
-      <c r="F124" s="13">
-        <f>'Balance Sheet'!F37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="n"/>
-      <c r="D125" s="16" t="n"/>
-      <c r="E125" s="16" t="n"/>
-      <c r="F125" s="16" t="n"/>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="16" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="n"/>
-      <c r="D126" s="15" t="n"/>
-      <c r="E126" s="15" t="n"/>
-      <c r="F126" s="15" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="n"/>
-      <c r="D127" s="16" t="n"/>
-      <c r="E127" s="16" t="n"/>
-      <c r="F127" s="16" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B127" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C127" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D127" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E127" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F127" s="13">
+        <f>'Balance Sheet'!F37</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n"/>
-      <c r="D128" s="15" t="n"/>
-      <c r="E128" s="15" t="n"/>
-      <c r="F128" s="15" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="n"/>
+      <c r="D128" s="16" t="n"/>
+      <c r="E128" s="16" t="n"/>
+      <c r="F128" s="16" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B129" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C129" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D129" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E129" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F129" s="13">
-        <f>'Balance Sheet'!F38</f>
-        <v/>
-      </c>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15" t="n"/>
+      <c r="E129" s="15" t="n"/>
+      <c r="F129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C130" s="16" t="n"/>
@@ -11188,7 +11248,7 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C131" s="15" t="n"/>
@@ -11199,56 +11259,56 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="n"/>
-      <c r="D132" s="16" t="n"/>
-      <c r="E132" s="16" t="n"/>
-      <c r="F132" s="16" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B132" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C132" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D132" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E132" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F132" s="13">
+        <f>'Balance Sheet'!F38</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C133" s="15" t="n"/>
-      <c r="D133" s="15" t="n"/>
-      <c r="E133" s="15" t="n"/>
-      <c r="F133" s="15" t="n"/>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C133" s="16" t="n"/>
+      <c r="D133" s="16" t="n"/>
+      <c r="E133" s="16" t="n"/>
+      <c r="F133" s="16" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B134" s="13">
-        <f>B124+B129</f>
-        <v/>
-      </c>
-      <c r="C134" s="13">
-        <f>C124+C129</f>
-        <v/>
-      </c>
-      <c r="D134" s="13">
-        <f>D124+D129</f>
-        <v/>
-      </c>
-      <c r="E134" s="13">
-        <f>E124+E129</f>
-        <v/>
-      </c>
-      <c r="F134" s="13">
-        <f>F124+F129</f>
-        <v/>
-      </c>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C135" s="16" t="n"/>
@@ -11259,7 +11319,7 @@
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C136" s="15" t="n"/>
@@ -11270,59 +11330,58 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="n"/>
-      <c r="E137" s="16" t="n"/>
-      <c r="F137" s="16" t="n"/>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B137" s="13">
+        <f>B127+B132</f>
+        <v/>
+      </c>
+      <c r="C137" s="13">
+        <f>C127+C132</f>
+        <v/>
+      </c>
+      <c r="D137" s="13">
+        <f>D127+D132</f>
+        <v/>
+      </c>
+      <c r="E137" s="13">
+        <f>E127+E132</f>
+        <v/>
+      </c>
+      <c r="F137" s="13">
+        <f>F127+F132</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C138" s="15" t="n"/>
-      <c r="D138" s="15" t="n"/>
-      <c r="E138" s="15" t="n"/>
-      <c r="F138" s="15" t="n"/>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="16" t="n"/>
+      <c r="E138" s="16" t="n"/>
+      <c r="F138" s="16" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B139" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C139" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D139" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E139" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F139" s="13">
-        <f>'Cash Flow Statement'!F38</f>
-        <v/>
-      </c>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="n"/>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
       <c r="C140" s="16" t="n"/>
       <c r="D140" s="16" t="n"/>
       <c r="E140" s="16" t="n"/>
@@ -11331,14 +11390,64 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments / Revenue</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="n"/>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
       <c r="C141" s="15" t="n"/>
       <c r="D141" s="15" t="n"/>
       <c r="E141" s="15" t="n"/>
       <c r="F141" s="15" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B142" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C142" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D142" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E142" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F142" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="n"/>
+      <c r="C143" s="16" t="n"/>
+      <c r="D143" s="16" t="n"/>
+      <c r="E143" s="16" t="n"/>
+      <c r="F143" s="16" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments / Revenue</t>
+        </is>
+      </c>
+      <c r="B144" s="15" t="n"/>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
